--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0001_ses-01_WMprob_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0001_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -1174,7 +1175,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B30" s="0">
         <v>0</v>
@@ -1338,7 +1339,7 @@
         <v>0.67799870170461318</v>
       </c>
       <c r="E34" s="0">
-        <v>0.4803245920224346</v>
+        <v>0.48032459202243461</v>
       </c>
       <c r="F34" s="0">
         <v>0.33657169886839106</v>
@@ -1473,7 +1474,7 @@
         <v>2.7061855670103068</v>
       </c>
       <c r="L37" s="0">
-        <v>1.5395141977420443</v>
+        <v>1.5395141977420444</v>
       </c>
     </row>
     <row r="38">
@@ -1616,7 +1617,7 @@
         <v>4.5730841333863763</v>
       </c>
       <c r="I41" s="0">
-        <v>4.4090484796727178</v>
+        <v>4.4090484796727179</v>
       </c>
       <c r="J41" s="0">
         <v>5.2815605447184639</v>
@@ -1812,7 +1813,7 @@
         <v>2.7788001472211974</v>
       </c>
       <c r="K46" s="0">
-        <v>4.3814432989690681</v>
+        <v>4.3814432989690682</v>
       </c>
       <c r="L46" s="0">
         <v>3.7150499175815597</v>
@@ -1905,7 +1906,7 @@
         <v>3.1803598828288431</v>
       </c>
       <c r="D49" s="0">
-        <v>3.1760151948645174</v>
+        <v>3.1760151948645175</v>
       </c>
       <c r="E49" s="0">
         <v>3.0830275366210182</v>
@@ -1987,7 +1988,7 @@
         <v>2.824666606999013</v>
       </c>
       <c r="F51" s="0">
-        <v>2.809009205690788</v>
+        <v>2.8090092056907881</v>
       </c>
       <c r="G51" s="0">
         <v>2.9169181251257266</v>
@@ -2025,7 +2026,7 @@
         <v>2.7303917181300137</v>
       </c>
       <c r="F52" s="0">
-        <v>2.6398137030164079</v>
+        <v>2.639813703016408</v>
       </c>
       <c r="G52" s="0">
         <v>2.3536511768255863</v>
@@ -2048,7 +2049,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>2.712415083193854</v>
+        <v>2.7124150831938541</v>
       </c>
       <c r="B53" s="0">
         <v>0.87719298245613953</v>
@@ -2063,7 +2064,7 @@
         <v>2.6086697097168745</v>
       </c>
       <c r="F53" s="0">
-        <v>2.5634028308408809</v>
+        <v>2.563402830840881</v>
       </c>
       <c r="G53" s="0">
         <v>2.1323677328505313</v>
@@ -2086,7 +2087,7 @@
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>2.6853401594959116</v>
+        <v>2.6853401594959117</v>
       </c>
       <c r="B54" s="0">
         <v>1.2280701754385954</v>
@@ -2165,7 +2166,7 @@
         <v>2.6188835286009624</v>
       </c>
       <c r="B56" s="0">
-        <v>2.1052631578947349</v>
+        <v>2.105263157894735</v>
       </c>
       <c r="C56" s="0">
         <v>2.2546570461202888</v>
@@ -2428,7 +2429,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.8140198877621327</v>
+        <v>1.8140198877621328</v>
       </c>
       <c r="B63" s="0">
         <v>1.1403508771929816</v>
@@ -2554,7 +2555,7 @@
         <v>0.83187074748154655</v>
       </c>
       <c r="E66" s="0">
-        <v>1.5453921656373983</v>
+        <v>1.5453921656373984</v>
       </c>
       <c r="F66" s="0">
         <v>1.4226976676490908</v>
@@ -2627,7 +2628,7 @@
         <v>1.1222561787494125</v>
       </c>
       <c r="D68" s="0">
-        <v>0.8006154881831069</v>
+        <v>0.80061548818310691</v>
       </c>
       <c r="E68" s="0">
         <v>1.4248635102479179</v>
@@ -2662,7 +2663,7 @@
         <v>0.17543859649122986</v>
       </c>
       <c r="C69" s="0">
-        <v>1.0575837887875938</v>
+        <v>1.0575837887875939</v>
       </c>
       <c r="D69" s="0">
         <v>0.69963695814200211</v>
@@ -2756,7 +2757,7 @@
         <v>1.1077657217519732</v>
       </c>
       <c r="I71" s="0">
-        <v>0.85003276995491583</v>
+        <v>0.85003276995491584</v>
       </c>
       <c r="J71" s="0">
         <v>0.88332719911667212</v>
@@ -2820,7 +2821,7 @@
         <v>0.47844589233765256</v>
       </c>
       <c r="E73" s="0">
-        <v>0.86697097168769865</v>
+        <v>0.86697097168769866</v>
       </c>
       <c r="F73" s="0">
         <v>0.98242549939962809</v>
@@ -2879,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="0">
-        <v>0.82729449818057343</v>
+        <v>0.82729449818057344</v>
       </c>
     </row>
     <row r="75">
@@ -3171,7 +3172,7 @@
         <v>0.32186682760008378</v>
       </c>
       <c r="H82" s="0">
-        <v>0.6248934840652226</v>
+        <v>0.62489348406522261</v>
       </c>
       <c r="I82" s="0">
         <v>0.33564378065977185</v>
@@ -3212,7 +3213,7 @@
         <v>0.46582968812134257</v>
       </c>
       <c r="I83" s="0">
-        <v>0.3237274334174095</v>
+        <v>0.32372743341740951</v>
       </c>
       <c r="J83" s="0">
         <v>0.44166359955833606</v>
@@ -3288,7 +3289,7 @@
         <v>0.38061694029426768</v>
       </c>
       <c r="I85" s="0">
-        <v>0.26414569720561631</v>
+        <v>0.26414569720561632</v>
       </c>
       <c r="J85" s="0">
         <v>0.5152741994847253</v>
@@ -3320,7 +3321,7 @@
         <v>0.40388603864206929</v>
       </c>
       <c r="G86" s="0">
-        <v>0.24140012070006014</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H86" s="0">
         <v>0.2556382434812246</v>
@@ -3536,7 +3537,7 @@
         <v>0.35087719298245584</v>
       </c>
       <c r="C92" s="0">
-        <v>0.040578754485854462</v>
+        <v>0.040578754485854463</v>
       </c>
       <c r="D92" s="0">
         <v>0.06010626788161464</v>
@@ -3563,7 +3564,7 @@
         <v>0.12886597938144317</v>
       </c>
       <c r="L92" s="0">
-        <v>0.1570615494666126</v>
+        <v>0.15706154946661261</v>
       </c>
     </row>
     <row r="93">
